--- a/results/six_week_reports_20261028/report_05_擴大候選搜尋的退步.xlsx
+++ b/results/six_week_reports_20261028/report_05_擴大候選搜尋的退步.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">必要對照!$A$1:$H$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">結果比較!$A$1:$H$74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">結果比較!$A$1:$H$78</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">設定與說明!$A$1:$H$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">必要對照!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">結果比較!$1:$3</definedName>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="124">
   <si>
     <t>第5次｜擴大候選搜尋的退步</t>
   </si>
@@ -57,15 +57,15 @@
     <t>本次成功／總數</t>
   </si>
   <si>
-    <t>差：後−前 pp</t>
+    <t>vs前一次 pp</t>
+  </si>
+  <si>
+    <t>vs論文 pp</t>
   </si>
   <si>
     <t>案例組成</t>
   </si>
   <si>
-    <t>批次</t>
-  </si>
-  <si>
     <t>Tongji／Plot1</t>
   </si>
   <si>
@@ -75,10 +75,7 @@
     <t>待補</t>
   </si>
   <si>
-    <t>10對×10seed</t>
-  </si>
-  <si>
-    <t>seed31–40</t>
+    <t>10對×10seed；31–40</t>
   </si>
   <si>
     <t>Tongji／Plot2</t>
@@ -111,7 +108,7 @@
     <t>150/150</t>
   </si>
   <si>
-    <t>15對×10seed</t>
+    <t>15對×10seed；31–40</t>
   </si>
   <si>
     <t>Tongji四Plot屬同一dataset，ETH屬另一dataset；兩者不混算誤差平均。前後均同配對與seed，失敗與缺輸出都保留。原論文門檻與分母未確認一致，100%只能作報告值參考。</t>
@@ -373,6 +370,12 @@
   </si>
   <si>
     <t>版本</t>
+  </si>
+  <si>
+    <t>候選pose數</t>
+  </si>
+  <si>
+    <t>精化數</t>
   </si>
   <si>
     <t>成功?</t>
@@ -466,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -481,13 +484,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -969,13 +975,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -999,13 +1005,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1420,137 +1426,142 @@
       <c r="B8" s="5">
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="7">
+        <f>(100/100-B8)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5">
         <v>1</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="7">
+        <f>(100/100-B9)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="7">
+        <f>(100/100-B10)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <f>(78/100-96/100)*100</f>
         <v>-17.999999999999993</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="7">
+        <f>(78/100-B11)*100</f>
+        <v>-21.999999999999996</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="45" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="5">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="E12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="7">
         <f>(150/150-150/150)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>28</v>
+      <c r="G12" s="7">
+        <f>(150/150-B12)*100</f>
+        <v>0.0</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="44" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1562,7 +1573,7 @@
     </row>
     <row r="17" spans="1:8" ht="28" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1577,41 +1588,41 @@
         <v>5</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>5.2558</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>16.81264811104687</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>2.886600508789238</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <v>2.886600508789238</v>
       </c>
       <c r="F19" s="5">
@@ -1623,23 +1634,23 @@
         <v>0.45077809110140454</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="7">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8">
         <v>11.4808</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>54.50497163856171</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <v>1.185415858528841</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <v>1.185415858528841</v>
       </c>
       <c r="F20" s="5">
@@ -1651,23 +1662,23 @@
         <v>0.8967479741369208</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="7">
+        <v>19</v>
+      </c>
+      <c r="B21" s="8">
         <v>4.8756</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>5.376450884068796</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <v>1.105659358968494</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <v>1.105659358968494</v>
       </c>
       <c r="F21" s="5">
@@ -1679,23 +1690,23 @@
         <v>0.7732259908588698</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="45" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="7">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8">
         <v>4.356</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <v>123.234678935483</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <v>103.4755735374764</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <v>864.7622010386872</v>
       </c>
       <c r="F22" s="4" t="s">
@@ -1706,23 +1717,23 @@
         <v>-197.52208471962516</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="45" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="7">
+        <v>24</v>
+      </c>
+      <c r="B23" s="8">
         <v>15.3427</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>12.62093021050369</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <v>0.6038135170910868</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <v>0.6038135171016774</v>
       </c>
       <c r="F23" s="5">
@@ -1734,12 +1745,12 @@
         <v>0.9606448984141202</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="44" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1751,7 +1762,7 @@
     </row>
     <row r="28" spans="1:8" ht="28" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1766,16 +1777,16 @@
         <v>5</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="45" customHeight="1">
@@ -1788,16 +1799,16 @@
       <c r="C30" s="5">
         <v>1</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="8">
         <v>2.886600508789238</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="8">
         <v>2.886600508789238</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="45" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" s="5">
         <v>1</v>
@@ -1805,16 +1816,16 @@
       <c r="C31" s="5">
         <v>1</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <v>1.185415858528841</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="8">
         <v>1.185415858528841</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="45" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" s="5">
         <v>1</v>
@@ -1822,16 +1833,16 @@
       <c r="C32" s="5">
         <v>1</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="8">
         <v>1.105659358968494</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="8">
         <v>1.105659358968494</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="45" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="5">
         <v>0.96</v>
@@ -1839,16 +1850,16 @@
       <c r="C33" s="5">
         <v>0.78</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="8">
         <v>103.4755735374764</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="8">
         <v>864.7622010386872</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="45" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B34" s="5">
         <v>1</v>
@@ -1856,10 +1867,10 @@
       <c r="C34" s="5">
         <v>1</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="8">
         <v>0.6038135170910868</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="8">
         <v>0.6038135171016774</v>
       </c>
     </row>
@@ -1938,7 +1949,7 @@
     </row>
     <row r="5" spans="1:8" ht="28" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1950,105 +1961,105 @@
     </row>
     <row r="6" spans="1:8" ht="40" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="45" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="46" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2060,7 +2071,7 @@
     </row>
     <row r="17" spans="1:8" ht="28" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -2075,88 +2086,88 @@
         <v>5</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>20.718</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>11.657</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="7">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8">
         <v>30.699</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>16.712</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="7">
+        <v>19</v>
+      </c>
+      <c r="B21" s="8">
         <v>4.5596</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>8.3584</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="45" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="7">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8">
         <v>19.522</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <v>9.451599999999999</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="45" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="7">
+        <v>24</v>
+      </c>
+      <c r="B23" s="8">
         <v>3.0405</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>8.699199999999999</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2168,7 +2179,7 @@
     </row>
     <row r="27" spans="1:8" ht="38" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2180,7 +2191,7 @@
     </row>
     <row r="28" spans="1:8" ht="38" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2192,7 +2203,7 @@
     </row>
     <row r="29" spans="1:8" ht="38" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2204,7 +2215,7 @@
     </row>
     <row r="30" spans="1:8" ht="52" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2291,7 +2302,7 @@
     </row>
     <row r="5" spans="1:8" ht="28" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2303,28 +2314,28 @@
     </row>
     <row r="6" spans="1:8" ht="40" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1">
@@ -2340,10 +2351,10 @@
       <c r="D7" s="4">
         <v>100</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>2.886600508789238</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>2.886600508789238</v>
       </c>
       <c r="G7" s="5">
@@ -2351,12 +2362,12 @@
         <v>0.0</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -2367,10 +2378,10 @@
       <c r="D8" s="4">
         <v>100</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>1.185415858528841</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>1.185415858528841</v>
       </c>
       <c r="G8" s="5">
@@ -2378,12 +2389,12 @@
         <v>0.0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -2394,10 +2405,10 @@
       <c r="D9" s="4">
         <v>100</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>1.105659358968494</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>1.105659358968494</v>
       </c>
       <c r="G9" s="5">
@@ -2405,12 +2416,12 @@
         <v>0.0</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
@@ -2421,10 +2432,10 @@
       <c r="D10" s="4">
         <v>77</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>2.207906820874123</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>2.207906820874123</v>
       </c>
       <c r="G10" s="5">
@@ -2432,12 +2443,12 @@
         <v>0.0</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="4">
         <v>0</v>
@@ -2448,10 +2459,10 @@
       <c r="D11" s="4">
         <v>150</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <v>0.6038135170910868</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>0.6038135171016774</v>
       </c>
       <c r="G11" s="5">
@@ -2459,12 +2470,12 @@
         <v>-1.7539477433418556e-11</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2479,160 +2490,160 @@
         <v>5</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="45" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>0.0356799496337756</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>0.0356799496337756</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <v>2.919916286083178</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <v>2.919916286083178</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <v>773.4700979200001</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <v>801.3975566300001</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="7">
+        <v>17</v>
+      </c>
+      <c r="B17" s="8">
         <v>0.055756468034214</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>0.055756468034214</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <v>1.035235466820431</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <v>1.035235466820431</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <v>943.13297948</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <v>942.32916675</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="7">
+        <v>19</v>
+      </c>
+      <c r="B18" s="8">
         <v>0.01954336228675064</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>0.01954336228675064</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <v>1.096707992766773</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <v>1.096707992766773</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="8">
         <v>543.56117039</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="8">
         <v>570.34143955</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="7">
+        <v>20</v>
+      </c>
+      <c r="B19" s="8">
         <v>3.646348975222628</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>28.79554128389449</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>104.9073571783149</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <v>874.4183854103326</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <v>461.19277371</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <v>2294.81875456</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="7">
+        <v>24</v>
+      </c>
+      <c r="B20" s="8">
         <v>0.05416013956404717</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>0.05416013956593288</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <v>0.4025727637157485</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <v>0.4025727637267302</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <v>578.4610634733333</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="8">
         <v>1440.75008394</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2647,41 +2658,41 @@
         <v>5</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="H24" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="45" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="8">
         <v>2.886600508789238</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="8">
         <v>2.886600508789238</v>
       </c>
       <c r="F25" s="4">
@@ -2691,23 +2702,23 @@
         <v>100</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="45" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="8">
         <v>1.185415858528841</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="8">
         <v>1.185415858528841</v>
       </c>
       <c r="F26" s="4">
@@ -2717,23 +2728,23 @@
         <v>100</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="45" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <v>1.105659358968494</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="8">
         <v>1.105659358968494</v>
       </c>
       <c r="F27" s="4">
@@ -2743,23 +2754,23 @@
         <v>100</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="45" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="D28" s="8">
         <v>172.5839561884964</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="8">
         <v>864.7622010386872</v>
       </c>
       <c r="F28" s="4">
@@ -2769,23 +2780,23 @@
         <v>100</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="45" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="7">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="8">
         <v>0.6038135170963769</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="8">
         <v>0.6038135171016774</v>
       </c>
       <c r="F29" s="4">
@@ -2795,12 +2806,12 @@
         <v>150</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="28" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2810,55 +2821,73 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:5" ht="40" customHeight="1">
+    <row r="33" spans="1:7" ht="40" customHeight="1">
       <c r="A33" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="45" customHeight="1">
+      <c r="G33" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="45" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B34" s="4">
+        <v>17</v>
+      </c>
+      <c r="C34" s="4">
+        <v>3</v>
+      </c>
+      <c r="D34" s="4">
         <v>1</v>
       </c>
-      <c r="C34" s="7">
+      <c r="E34" s="8">
         <v>0.166977824126439</v>
       </c>
-      <c r="D34" s="7">
+      <c r="F34" s="8">
         <v>0.0856039352913584</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="45" customHeight="1">
+      <c r="G34" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="45" customHeight="1">
       <c r="A35" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="4">
+        <v>134</v>
+      </c>
+      <c r="C35" s="4">
+        <v>8</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.3377234445518996</v>
+      </c>
+      <c r="F35" s="8">
+        <v>45.93514000954847</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="B35" s="4">
-        <v>0</v>
-      </c>
-      <c r="C35" s="7">
-        <v>0.3377234445518996</v>
-      </c>
-      <c r="D35" s="7">
-        <v>45.93514000954847</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
